--- a/data/trans_orig/P41E_2023_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P41E_2023_R-Habitat-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que en el último año sus relaciones sexuales han sido satisfactorias para ambas partes en 2023</t>
+          <t>Población que en el último año sus relaciones sexuales han sido satisfactorias para ambas partes en 2023 (tasa de respuesta: 69,32%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>39392</t>
+          <t>38669</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>63098</t>
+          <t>63000</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>18,21%</t>
+          <t>18,18%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>39903</t>
+          <t>39157</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>58389</t>
+          <t>56726</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>12,08%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>18,02%</t>
+          <t>17,51%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>81062</t>
+          <t>83181</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>111600</t>
+          <t>112795</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>12,4%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>16,64%</t>
+          <t>16,82%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>283434</t>
+          <t>283532</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>307140</t>
+          <t>307863</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>81,79%</t>
+          <t>81,82%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>88,63%</t>
+          <t>88,84%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>265667</t>
+          <t>267330</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>284153</t>
+          <t>284899</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>81,98%</t>
+          <t>82,49%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>87,69%</t>
+          <t>87,92%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>558988</t>
+          <t>557793</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>589526</t>
+          <t>587407</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>83,36%</t>
+          <t>83,18%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>87,91%</t>
+          <t>87,6%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>17557</t>
+          <t>17282</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>75474</t>
+          <t>75402</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>51635</t>
+          <t>52174</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>74833</t>
+          <t>73747</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>15,69%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>55156</t>
+          <t>58347</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>144706</t>
+          <t>146125</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>11,98%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>673914</t>
+          <t>673986</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>731831</t>
+          <t>732106</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>89,93%</t>
+          <t>89,94%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,69%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>395104</t>
+          <t>396190</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>418302</t>
+          <t>417763</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>84,08%</t>
+          <t>84,31%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>89,01%</t>
+          <t>88,9%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1074619</t>
+          <t>1073200</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1164169</t>
+          <t>1160978</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,13%</t>
+          <t>88,02%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,48%</t>
+          <t>95,21%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8197</t>
+          <t>8363</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>20424</t>
+          <t>20531</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1686</t>
+          <t>1436</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>17666</t>
+          <t>17770</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7942</t>
+          <t>8208</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>34796</t>
+          <t>34701</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,22%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>210128</t>
+          <t>210021</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>222355</t>
+          <t>222189</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,14%</t>
+          <t>91,09%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,44%</t>
+          <t>96,37%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>416152</t>
+          <t>416048</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>432132</t>
+          <t>432382</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>95,9%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,61%</t>
+          <t>99,67%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>629574</t>
+          <t>629669</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>656428</t>
+          <t>656162</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,76%</t>
+          <t>94,78%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,76%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>51981</t>
+          <t>52005</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>77846</t>
+          <t>78320</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1779,7 +1779,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,01%</t>
+          <t>18,12%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>53261</t>
+          <t>52951</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>75067</t>
+          <t>76875</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>12,05%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>17,49%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>111606</t>
+          <t>112854</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>146073</t>
+          <t>148390</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>12,95%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,76%</t>
+          <t>17,02%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>354343</t>
+          <t>353869</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>380208</t>
+          <t>380184</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>81,99%</t>
+          <t>81,88%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>364428</t>
+          <t>362620</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>386234</t>
+          <t>386544</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>82,92%</t>
+          <t>82,51%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>87,88%</t>
+          <t>87,95%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>725611</t>
+          <t>723294</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>760078</t>
+          <t>758830</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>83,24%</t>
+          <t>82,98%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>87,2%</t>
+          <t>87,05%</t>
         </is>
       </c>
     </row>
@@ -2102,12 +2102,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>102485</t>
+          <t>111245</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>209182</t>
+          <t>214306</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,12 +2117,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>120512</t>
+          <t>115136</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>216301</t>
+          <t>216997</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>13,01%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>271699</t>
+          <t>259713</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>413790</t>
+          <t>414366</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>12,09%</t>
         </is>
       </c>
     </row>
@@ -2215,12 +2215,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1549479</t>
+          <t>1544355</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1656176</t>
+          <t>1647416</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>88,11%</t>
+          <t>87,81%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,17%</t>
+          <t>93,67%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1451005</t>
+          <t>1450309</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1546794</t>
+          <t>1552170</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>87,03%</t>
+          <t>86,99%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>92,77%</t>
+          <t>93,09%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3012177</t>
+          <t>3011601</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>3154268</t>
+          <t>3166254</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,12 +2300,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>87,92%</t>
+          <t>87,91%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,07%</t>
+          <t>92,42%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P41E_2023_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P41E_2023_R-Habitat-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>49459</t>
+          <t>51421</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>38669</t>
+          <t>39914</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>63000</t>
+          <t>64576</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>13,99%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>18,18%</t>
+          <t>17,57%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>47761</t>
+          <t>51192</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>39157</t>
+          <t>41176</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>56726</t>
+          <t>61803</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>14,85%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>11,94%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>17,51%</t>
+          <t>17,92%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>97220</t>
+          <t>102613</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>83181</t>
+          <t>87632</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>112795</t>
+          <t>119524</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>14,4%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>16,82%</t>
+          <t>16,78%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>297073</t>
+          <t>316190</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>283532</t>
+          <t>303035</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>307863</t>
+          <t>327697</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>85,73%</t>
+          <t>86,01%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>81,82%</t>
+          <t>82,43%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>88,84%</t>
+          <t>89,14%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>276295</t>
+          <t>293630</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>267330</t>
+          <t>283019</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>284899</t>
+          <t>303646</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>85,26%</t>
+          <t>85,15%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>82,49%</t>
+          <t>82,08%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>87,92%</t>
+          <t>88,06%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>573368</t>
+          <t>609821</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>557793</t>
+          <t>592910</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>587407</t>
+          <t>624802</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>85,5%</t>
+          <t>85,6%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>83,18%</t>
+          <t>83,22%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>87,6%</t>
+          <t>87,7%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>346532</t>
+          <t>367611</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>346532</t>
+          <t>367611</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>346532</t>
+          <t>367611</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>324056</t>
+          <t>344822</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>324056</t>
+          <t>344822</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>324056</t>
+          <t>344822</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>670588</t>
+          <t>712434</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>670588</t>
+          <t>712434</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>670588</t>
+          <t>712434</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,32 +1068,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>47570</t>
+          <t>51968</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>17282</t>
+          <t>40232</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>75402</t>
+          <t>65251</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>11,64%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>62695</t>
+          <t>69482</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>52174</t>
+          <t>58121</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>73747</t>
+          <t>84932</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>11,24%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>16,42%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>110265</t>
+          <t>121450</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>58347</t>
+          <t>104862</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>146125</t>
+          <t>139952</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>12,99%</t>
         </is>
       </c>
     </row>
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>701818</t>
+          <t>508537</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>673986</t>
+          <t>495254</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>732106</t>
+          <t>520273</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>93,65%</t>
+          <t>90,73%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>89,94%</t>
+          <t>88,36%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>92,82%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>407242</t>
+          <t>447696</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>396190</t>
+          <t>432246</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>417763</t>
+          <t>459057</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>86,66%</t>
+          <t>86,57%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>84,31%</t>
+          <t>83,58%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>88,9%</t>
+          <t>88,76%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1109060</t>
+          <t>956233</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1073200</t>
+          <t>937731</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1160978</t>
+          <t>972821</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>90,96%</t>
+          <t>88,73%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,02%</t>
+          <t>87,01%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,21%</t>
+          <t>90,27%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>749388</t>
+          <t>560505</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>749388</t>
+          <t>560505</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>749388</t>
+          <t>560505</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>469937</t>
+          <t>517178</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>469937</t>
+          <t>517178</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>469937</t>
+          <t>517178</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1219325</t>
+          <t>1077683</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1219325</t>
+          <t>1077683</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1219325</t>
+          <t>1077683</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>12994</t>
+          <t>14327</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8363</t>
+          <t>8312</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>20531</t>
+          <t>21743</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>8095</t>
+          <t>9445</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1436</t>
+          <t>5286</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>17770</t>
+          <t>15063</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>21088</t>
+          <t>23772</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>8208</t>
+          <t>16255</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>34701</t>
+          <t>32116</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,94%</t>
         </is>
       </c>
     </row>
@@ -1524,32 +1524,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>217558</t>
+          <t>253456</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>210021</t>
+          <t>246040</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>222189</t>
+          <t>259471</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>94,36%</t>
+          <t>94,65%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,09%</t>
+          <t>91,88%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>96,9%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>425723</t>
+          <t>263584</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>416048</t>
+          <t>257966</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>432382</t>
+          <t>267743</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>96,54%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,9%</t>
+          <t>94,48%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,67%</t>
+          <t>98,06%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>643282</t>
+          <t>517041</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>629669</t>
+          <t>508697</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>656162</t>
+          <t>524558</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>95,6%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,78%</t>
+          <t>94,06%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>96,99%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>230552</t>
+          <t>267783</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>230552</t>
+          <t>267783</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>230552</t>
+          <t>267783</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>433818</t>
+          <t>273029</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>433818</t>
+          <t>273029</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>433818</t>
+          <t>273029</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>664370</t>
+          <t>540813</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>664370</t>
+          <t>540813</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>664370</t>
+          <t>540813</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>64348</t>
+          <t>68709</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>52005</t>
+          <t>54380</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>78320</t>
+          <t>83359</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>14,84%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,12%</t>
+          <t>18,0%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>64556</t>
+          <t>70520</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>52951</t>
+          <t>58815</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>76875</t>
+          <t>84538</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>14,69%</t>
+          <t>14,6%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,49%</t>
+          <t>17,5%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>128904</t>
+          <t>139230</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>112854</t>
+          <t>122968</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>148390</t>
+          <t>158813</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>14,79%</t>
+          <t>14,72%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>17,02%</t>
+          <t>16,79%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>367841</t>
+          <t>394330</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>353869</t>
+          <t>379680</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>380184</t>
+          <t>408659</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>85,11%</t>
+          <t>85,16%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>81,88%</t>
+          <t>82,0%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>87,97%</t>
+          <t>88,26%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>374939</t>
+          <t>412428</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>362620</t>
+          <t>398410</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>386544</t>
+          <t>424133</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>85,31%</t>
+          <t>85,4%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>82,51%</t>
+          <t>82,5%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>87,95%</t>
+          <t>87,82%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>742780</t>
+          <t>806757</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>723294</t>
+          <t>787174</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>758830</t>
+          <t>823019</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>85,21%</t>
+          <t>85,28%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>82,98%</t>
+          <t>83,21%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>87,05%</t>
+          <t>87,0%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>432189</t>
+          <t>463039</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>432189</t>
+          <t>463039</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>432189</t>
+          <t>463039</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>439495</t>
+          <t>482948</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>439495</t>
+          <t>482948</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>439495</t>
+          <t>482948</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>871684</t>
+          <t>945987</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>871684</t>
+          <t>945987</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>871684</t>
+          <t>945987</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,32 +2097,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>174371</t>
+          <t>186425</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>111245</t>
+          <t>163464</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>214306</t>
+          <t>210543</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>11,24%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>12,69%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,32 +2132,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>183107</t>
+          <t>200639</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>115136</t>
+          <t>179746</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>216997</t>
+          <t>222327</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>12,4%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>13,74%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>357478</t>
+          <t>387064</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>259713</t>
+          <t>356631</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>414366</t>
+          <t>418249</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>12,76%</t>
         </is>
       </c>
     </row>
@@ -2210,32 +2210,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1584290</t>
+          <t>1472513</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1544355</t>
+          <t>1448395</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1647416</t>
+          <t>1495474</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>90,09%</t>
+          <t>88,76%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>87,81%</t>
+          <t>87,31%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>93,67%</t>
+          <t>90,15%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,32 +2245,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1484199</t>
+          <t>1417339</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1450309</t>
+          <t>1395651</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1552170</t>
+          <t>1438232</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>89,02%</t>
+          <t>87,6%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>86,99%</t>
+          <t>86,26%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,09%</t>
+          <t>88,89%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>3068489</t>
+          <t>2889852</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3011601</t>
+          <t>2858667</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>3166254</t>
+          <t>2920285</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>89,57%</t>
+          <t>88,19%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>87,91%</t>
+          <t>87,24%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,42%</t>
+          <t>89,12%</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1758661</t>
+          <t>1658938</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1758661</t>
+          <t>1658938</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1758661</t>
+          <t>1658938</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1667306</t>
+          <t>1617978</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1667306</t>
+          <t>1617978</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1667306</t>
+          <t>1617978</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>3425967</t>
+          <t>3276916</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>3425967</t>
+          <t>3276916</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>3425967</t>
+          <t>3276916</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">

--- a/data/trans_orig/P41E_2023_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P41E_2023_R-Habitat-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que en el último año sus relaciones sexuales han sido satisfactorias para ambas partes en 2023 (tasa de respuesta: 69,32%)</t>
+          <t>Población que en el último año declara que sus relaciones sexuales no han sido satisfactorias para ambas partes (bastante en desacuerdo/totalmente en desacuerdo) en 2023 (tasa de respuesta: 69,32%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
